--- a/backend/exports/payments.xlsx
+++ b/backend/exports/payments.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="76">
   <si>
     <t>Transaction ID</t>
   </si>
@@ -227,6 +227,18 @@
   </si>
   <si>
     <t>27/6/2026, 6:25:51 pm</t>
+  </si>
+  <si>
+    <t>pay_TdBs9dY8EJPoHd</t>
+  </si>
+  <si>
+    <t>WT-228400</t>
+  </si>
+  <si>
+    <t>Nit Bhor</t>
+  </si>
+  <si>
+    <t>17/9/2026, 11:13:37 pm</t>
   </si>
 </sst>
 </file>
@@ -603,7 +615,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
@@ -1090,6 +1102,38 @@
         <v>71</v>
       </c>
     </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>72</v>
+      </c>
+      <c r="B18" t="s">
+        <v>73</v>
+      </c>
+      <c r="C18" t="s">
+        <v>74</v>
+      </c>
+      <c r="D18" t="s">
+        <v>18</v>
+      </c>
+      <c r="E18" t="s">
+        <v>14</v>
+      </c>
+      <c r="F18">
+        <v>15000</v>
+      </c>
+      <c r="G18" t="s">
+        <v>39</v>
+      </c>
+      <c r="H18">
+        <v>157</v>
+      </c>
+      <c r="I18">
+        <v>15000</v>
+      </c>
+      <c r="J18" t="s">
+        <v>75</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>

--- a/backend/exports/payments.xlsx
+++ b/backend/exports/payments.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="80">
   <si>
     <t>Transaction ID</t>
   </si>
@@ -239,6 +239,18 @@
   </si>
   <si>
     <t>17/9/2026, 11:13:37 pm</t>
+  </si>
+  <si>
+    <t>pay_Tl3ZEXp9JkH6tR</t>
+  </si>
+  <si>
+    <t>WT-656662</t>
+  </si>
+  <si>
+    <t>sczdczd zdsczdczs</t>
+  </si>
+  <si>
+    <t>7/10/2026, 8:18:05 pm</t>
   </si>
 </sst>
 </file>
@@ -615,7 +627,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
@@ -1134,6 +1146,38 @@
         <v>75</v>
       </c>
     </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>76</v>
+      </c>
+      <c r="B19" t="s">
+        <v>77</v>
+      </c>
+      <c r="C19" t="s">
+        <v>78</v>
+      </c>
+      <c r="D19" t="s">
+        <v>18</v>
+      </c>
+      <c r="E19" t="s">
+        <v>14</v>
+      </c>
+      <c r="F19">
+        <v>32000</v>
+      </c>
+      <c r="G19" t="s">
+        <v>39</v>
+      </c>
+      <c r="H19">
+        <v>335</v>
+      </c>
+      <c r="I19">
+        <v>32000</v>
+      </c>
+      <c r="J19" t="s">
+        <v>79</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>

--- a/backend/exports/payments.xlsx
+++ b/backend/exports/payments.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="84">
   <si>
     <t>Transaction ID</t>
   </si>
@@ -251,6 +251,18 @@
   </si>
   <si>
     <t>7/10/2026, 8:18:05 pm</t>
+  </si>
+  <si>
+    <t>pay_TlIeYuZBXNwcJA</t>
+  </si>
+  <si>
+    <t>WT-808282</t>
+  </si>
+  <si>
+    <t>aasasd asadasdad</t>
+  </si>
+  <si>
+    <t>8/10/2026, 11:03:29 am</t>
   </si>
 </sst>
 </file>
@@ -627,7 +639,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
@@ -1178,6 +1190,38 @@
         <v>79</v>
       </c>
     </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>80</v>
+      </c>
+      <c r="B20" t="s">
+        <v>81</v>
+      </c>
+      <c r="C20" t="s">
+        <v>82</v>
+      </c>
+      <c r="D20" t="s">
+        <v>18</v>
+      </c>
+      <c r="E20" t="s">
+        <v>14</v>
+      </c>
+      <c r="F20">
+        <v>14500</v>
+      </c>
+      <c r="G20" t="s">
+        <v>39</v>
+      </c>
+      <c r="H20">
+        <v>152</v>
+      </c>
+      <c r="I20">
+        <v>14500</v>
+      </c>
+      <c r="J20" t="s">
+        <v>83</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
